--- a/etf_holdings/2026-09-24_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-09-24_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,97 +486,133 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>9939</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>宏全</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>4.87%</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.08%</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>4.62%</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-0.25%</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>89118000</v>
+      </c>
       <c r="K2" t="n">
-        <v>180000</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
+        <v>87118000</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-2,000,000</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-09-23_00400A_full_holdings.xlsx</t>
+          <t>2026-09-23_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>元大金</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>台達電</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>台達電</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.53%</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+          <t>4.81%</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>4.82%</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
       <c r="J3" t="n">
-        <v>2241040</v>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+        <v>7420000</v>
+      </c>
+      <c r="K3" t="n">
+        <v>7320000</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-100,000</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-09-23_00400A_full_holdings.xlsx</t>
+          <t>2026-09-23_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -591,109 +627,6751 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>5.41%</t>
+          <t>4.91%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>5.04%</t>
+          <t>4.95%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>190000</v>
+        <v>25107000</v>
       </c>
       <c r="K4" t="n">
-        <v>173000</v>
+        <v>24757000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-17,000</t>
+          <t>-350,000</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-09-23_00400A_full_holdings.xlsx</t>
+          <t>2026-09-23_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>00981A</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>10.12%</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>9.77%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-0.35%</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>11864000</v>
+      </c>
+      <c r="K5" t="n">
+        <v>11464000</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-400,000</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-09-23_00981A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>00981A</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>4.17%</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>4.09%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-0.08%</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>6464000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6264000</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-200,000</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-09-23_00981A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>00981A</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.65%</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.62%</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-0.03%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1663000</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1634000</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-29,000</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-09-23_00981A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>00981A</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>8.14%</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>8.09%</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-0.05%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>4750000</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4650000</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-100,000</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-09-23_00981A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>00981A</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2449</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1.36%</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1.39%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>13138450</v>
+      </c>
+      <c r="K9" t="n">
+        <v>12938450</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-200,000</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-09-23_00981A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>00981A</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>9.18%</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>9.26%</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>+0.08%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>5186000</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5086000</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-100,000</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-09-23_00981A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>00981A</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>7.05%</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>7.21%</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>+0.16%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>5949000</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5889000</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-60,000</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-09-23_00981A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>00981A</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>8.04%</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>8.20%</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>+0.16%</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>20300000</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20100000</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-200,000</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-09-23_00981A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>00981A</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>3264</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.45%</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.42%</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>-0.03%</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>5182000</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4982000</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>-200,000</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-09-23_00981A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>00981A</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1.18%</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>1.14%</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-0.04%</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>413000</v>
+      </c>
+      <c r="K14" t="n">
+        <v>388000</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>-25,000</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-09-23_00981A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>00981A</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>3653</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>5.50%</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>5.96%</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>+0.46%</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>2512000</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2502000</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>-10,000</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-09-23_00981A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>00981A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>3665</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>3.15%</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>3.12%</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>-0.03%</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>3943848</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3876848</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>-67,000</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-09-23_00981A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>00981A</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>3.66%</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>3.36%</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>-0.30%</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>15466000</v>
+      </c>
+      <c r="K17" t="n">
+        <v>13966000</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>-1,500,000</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-09-23_00981A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>00981A</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>4958</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0.57%</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.57%</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>3543000</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3483000</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-60,000</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-09-23_00981A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>00981A</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>5274</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1.44%</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>1.15%</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-0.29%</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>207900</v>
+      </c>
+      <c r="K19" t="n">
+        <v>168900</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>-39,000</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-09-23_00981A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>00981A</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>6191</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>精成科</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>精成科</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0.11%</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>0.11%</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>3988000</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3921000</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>-67,000</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-09-23_00981A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>00981A</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>4.88%</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>4.66%</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-0.22%</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>2544000</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2499000</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>-45,000</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-09-23_00981A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>00981A</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>6271</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>同欣電</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>同欣電</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0.17%</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>0.17%</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>2222000</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2185000</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-37,000</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-09-23_00981A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>00981A</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2.96%</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>3.03%</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>+0.07%</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>5936000</v>
+      </c>
+      <c r="K23" t="n">
+        <v>5886000</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-50,000</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-09-23_00981A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>00981A</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>6278</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>台表科</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>台表科</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0.23%</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>0.23%</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>3248000</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3193000</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>-55,000</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-09-23_00981A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>00981A</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>6510</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>精測</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>精測</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0.30%</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>0.29%</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>256000</v>
+      </c>
+      <c r="K25" t="n">
+        <v>251000</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>-5,000</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2026-09-23_00981A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>00981A</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0.19%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>0.19%</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>95000</v>
+      </c>
+      <c r="K26" t="n">
+        <v>93000</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>-2,000</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-09-23_00981A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>00981A</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>3.69%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>3.55%</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>-0.14%</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>5138561</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4873561</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>-265,000</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-09-23_00981A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>00981A</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1.57%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>1.46%</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>-0.11%</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>1773000</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1673000</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>-100,000</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-09-23_00981A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>00981A</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>3.73%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>3.82%</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>+0.09%</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>9037000</v>
+      </c>
+      <c r="K29" t="n">
+        <v>8937000</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>-100,000</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-09-23_00981A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>00981A</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>8210</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>勤誠</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>勤誠</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>1159000</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1139000</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>-20,000</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-09-23_00981A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>00981A</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>8996</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>0.25%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>0.25%</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>485000</v>
+      </c>
+      <c r="K31" t="n">
+        <v>476000</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>-9,000</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2026-09-23_00981A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>00991A</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>川湖科技</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>川湖科技</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>7.66%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>-7.68%</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>490000</v>
+      </c>
+      <c r="K32" t="n">
+        <v>480000</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>-10,000</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2026-09-23_00991A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>00991A</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>智邦科技</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>智邦科技</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1.91%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>-1.91%</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>800000</v>
+      </c>
+      <c r="K33" t="n">
+        <v>740000</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>-60,000</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-09-23_00991A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>00991A</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>台光電子</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>台光電子</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>8.74%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+0.05%</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>-8.69%</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>1380000</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1350000</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>-30,000</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-09-23_00991A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>00991A</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>南亞科技</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>南亞科技</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>8.77%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-0.20%</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>-8.97%</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>13500000</v>
+      </c>
+      <c r="K35" t="n">
+        <v>13000000</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>-500,000</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-09-23_00991A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>00991A</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>3189</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>景碩科技</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>景碩科技</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>4.86%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+0.31%</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>-4.55%</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>4250000</v>
+      </c>
+      <c r="K36" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>150,000</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-09-23_00991A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>00991A</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>日月光投</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>日月光投</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2.06%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>-2.04%</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>2350000</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2030000</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>-320,000</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-09-23_00991A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>00991A</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>旺矽科技</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>旺矽科技</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1.99%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-0.07%</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>-2.06%</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>280000</v>
+      </c>
+      <c r="K38" t="n">
+        <v>250000</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>-30,000</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-09-23_00991A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2395</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2.01%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>1.56%</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>-0.45%</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>1454000</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1128000</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>-326,000</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-09-23_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2.01%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>1.60%</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>-0.41%</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>13500000</v>
+      </c>
+      <c r="K40" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>-3,500,000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-09-23_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>6.28%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>5.38%</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>-0.90%</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="K41" t="n">
+        <v>52000000</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>-8,000,000</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-09-23_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>13.73%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>12.81%</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>-0.92%</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>8400000</v>
+      </c>
+      <c r="K42" t="n">
+        <v>7700000</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>-700,000</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-09-23_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>0.71%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>0.48%</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>-0.23%</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>470000</v>
+      </c>
+      <c r="K43" t="n">
+        <v>310000</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>-160,000</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-09-23_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>5.25%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>4.75%</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>-0.50%</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>-200,000</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-09-23_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>3189</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>景碩</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>景碩</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2.37%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2.79%</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>+0.42%</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="K45" t="n">
+        <v>4310000</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>310,000</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-09-23_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2.52%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2.51%</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>1827956</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1767956</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>-60,000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-09-23_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>7769</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>鴻勁</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>鴻勁</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.31%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>-0.31%</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>80000</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>-79,000</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-09-23_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2.19%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2.42%</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>+0.23%</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>2770000</v>
+      </c>
+      <c r="K48" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>130,000</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-09-23_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>3131</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>弘塑</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-09-23_00992A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>3.38%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>4.59%</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>+1.21%</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>268000</v>
+      </c>
+      <c r="K50" t="n">
+        <v>344000</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>76,000</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-09-23_00992A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>6584</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>南俊國際</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>南俊國際</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2.91%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2.85%</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>-0.06%</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>2231000</v>
+      </c>
+      <c r="K51" t="n">
+        <v>2213000</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>-18,000</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-09-23_00992A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>8.99%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>6.89%</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>-2.10%</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>480000</v>
+      </c>
+      <c r="K52" t="n">
+        <v>344000</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>-136,000</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-09-23_00405A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>9.21%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>6.88%</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>-2.33%</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>304000</v>
+      </c>
+      <c r="K53" t="n">
+        <v>213000</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>-91,000</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-09-23_00405A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1560</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>中砂</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>0.86%</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="n">
+        <v>93000</v>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>東和鋼鐵</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>0.52%</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="n">
+        <v>628000</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>大成鋼</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>0.19%</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="n">
+        <v>416000</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>光寶科技</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>0.22%</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="n">
+        <v>80000</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>0.32%</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="n">
+        <v>14000</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2395</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>0.52%</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="n">
+        <v>76000</v>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2412</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>中華電</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>0.45%</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="n">
+        <v>319000</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2603</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>長榮海運</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>0.29%</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="n">
+        <v>121000</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2606</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>裕民</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>0.33%</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="n">
+        <v>446000</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2618</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>長榮航</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>0.18%</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="n">
+        <v>429000</v>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>雙鴻科技</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>0.54%</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="n">
+        <v>35000</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>3406</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>玉晶光</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>0.25%</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="n">
+        <v>29000</v>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>3491</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>昇達科技</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>0.15%</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>台勝科</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>0.30%</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="n">
+        <v>70000</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>0.51%</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="n">
+        <v>76000</v>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>4904</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>遠傳</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>0.24%</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="n">
+        <v>237000</v>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>6213</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>聯茂</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="n">
+        <v>95000</v>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>6505</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>台塑石化</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>0.29%</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="n">
+        <v>339000</v>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2337</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>旺宏</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>0.73%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="n">
+        <v>637000</v>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>金像電子</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2.01%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="n">
+        <v>200000</v>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2449</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>0.41%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="n">
+        <v>134000</v>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>3036</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>文曄</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>0.62%</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="n">
+        <v>312000</v>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>3042</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>晶技</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="n">
+        <v>196000</v>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>3131</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>弘塑科技</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>0.56%</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="n">
+        <v>24000</v>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>1.75%</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="n">
+        <v>1003000</v>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>3264</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>欣銓</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>1.49%</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="n">
+        <v>559000</v>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>3702</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>大聯大</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>0.39%</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="n">
+        <v>359000</v>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>亞翔工程</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>1.14%</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="n">
+        <v>165000</v>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>6239</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>力成</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>0.47%</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="n">
+        <v>165000</v>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>6415</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>矽力*-KY</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>0.39%</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="n">
+        <v>93000</v>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>6510</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>精測</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>0.64%</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="n">
+        <v>18000</v>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>1.78%</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="n">
+        <v>32000</v>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>8210</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>勤誠興業</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>0.65%</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="n">
+        <v>75000</v>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>8996</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>2.14%</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="n">
+        <v>134000</v>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>3.64%</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>1.26%</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>-2.38%</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>1629000</v>
+      </c>
+      <c r="K88" t="n">
+        <v>571000</v>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>-1,058,000</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>3.43%</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>2.41%</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>-1.02%</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>28000</v>
+      </c>
+      <c r="K89" t="n">
+        <v>20000</v>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>-8,000</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>1.85%</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>2.85%</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>+1.00%</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>1197000</v>
+      </c>
+      <c r="K90" t="n">
+        <v>1835000</v>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>638,000</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2313</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>華通</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>華通</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>0.24%</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>-0.11%</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>165000</v>
+      </c>
+      <c r="K91" t="n">
+        <v>110000</v>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>-55,000</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2327</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>0.90%</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>2.03%</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>+1.13%</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>163000</v>
+      </c>
+      <c r="K92" t="n">
+        <v>365000</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>202,000</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>8.00%</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>8.42%</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>+0.42%</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>336000</v>
+      </c>
+      <c r="K93" t="n">
+        <v>347000</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>華邦電子</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>華邦電子</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>2.08%</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>2.06%</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>1260000</v>
+      </c>
+      <c r="K94" t="n">
+        <v>1228000</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>-32,000</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>2.55%</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>2.37%</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>-0.18%</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>138000</v>
+      </c>
+      <c r="K95" t="n">
+        <v>129000</v>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>-9,000</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2347</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>聯強</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>聯強</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>0.39%</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>0.43%</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>+0.04%</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>448000</v>
+      </c>
+      <c r="K96" t="n">
+        <v>465000</v>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>17,000</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>台光電子</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>台光電子</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>4.60%</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>4.88%</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>+0.28%</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>98000</v>
+      </c>
+      <c r="K97" t="n">
+        <v>100000</v>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>3.19%</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>3.07%</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>-0.12%</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>665000</v>
+      </c>
+      <c r="K98" t="n">
+        <v>613000</v>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>-52,000</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>6.66%</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>6.60%</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>-0.06%</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>133000</v>
+      </c>
+      <c r="K99" t="n">
+        <v>131000</v>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>-2,000</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>大立光電</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>大立光電</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>1.80%</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>1.56%</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>-0.24%</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>29000</v>
+      </c>
+      <c r="K100" t="n">
+        <v>26000</v>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>-3,000</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>3.44%</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>5.33%</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>+1.89%</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>105000</v>
+      </c>
+      <c r="K101" t="n">
+        <v>158000</v>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>53,000</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>3.30%</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>5.54%</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>+2.24%</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>305000</v>
+      </c>
+      <c r="K102" t="n">
+        <v>492000</v>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>187,000</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>健鼎科技</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>健鼎科技</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>0.47%</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>0.28%</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>-0.19%</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>90000</v>
+      </c>
+      <c r="K103" t="n">
+        <v>54000</v>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>-36,000</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>3081</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>聯亞光電</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>聯亞光電</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>1.26%</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>0.49%</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>-0.77%</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>46000</v>
+      </c>
+      <c r="K104" t="n">
+        <v>19000</v>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>-27,000</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>3189</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>景碩科技</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>景碩科技</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>2.34%</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>3.77%</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>+1.43%</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>266000</v>
+      </c>
+      <c r="K105" t="n">
+        <v>428000</v>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>162,000</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>創意電子</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>創意電子</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>4.05%</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>5.29%</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>+1.24%</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>50000</v>
+      </c>
+      <c r="K106" t="n">
+        <v>65000</v>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>15,000</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>3665</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>2.15%</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>1.89%</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>-0.26%</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>99000</v>
+      </c>
+      <c r="K107" t="n">
+        <v>83000</v>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>-16,000</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>4958</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>1.83%</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>1.17%</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>-0.66%</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>388000</v>
+      </c>
+      <c r="K108" t="n">
+        <v>255000</v>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>-133,000</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>5274</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>信驊科技</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>信驊科技</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>3.15%</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>4.06%</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>+0.91%</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>15600</v>
+      </c>
+      <c r="K109" t="n">
+        <v>20600</v>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>5289</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>宜鼎國際</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>宜鼎國際</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>0.66%</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>0.04%</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>-0.62%</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>52872</v>
+      </c>
+      <c r="K110" t="n">
+        <v>2872</v>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>-50,000</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>6147</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>頎邦</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>頎邦</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>0.80%</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>0.24%</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>-0.56%</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>378000</v>
+      </c>
+      <c r="K111" t="n">
+        <v>113000</v>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>-265,000</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>3.98%</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>4.37%</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>+0.39%</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>77000</v>
+      </c>
+      <c r="K112" t="n">
+        <v>80000</v>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>2.55%</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>2.25%</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>-0.30%</t>
+        </is>
+      </c>
+      <c r="J113" t="n">
+        <v>183000</v>
+      </c>
+      <c r="K113" t="n">
+        <v>159000</v>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>-24,000</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>2.23%</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>4.40%</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>+2.17%</t>
+        </is>
+      </c>
+      <c r="J114" t="n">
+        <v>109191</v>
+      </c>
+      <c r="K114" t="n">
+        <v>215191</v>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>106,000</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>1.74%</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>0.56%</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>-1.18%</t>
+        </is>
+      </c>
+      <c r="J115" t="n">
+        <v>72000</v>
+      </c>
+      <c r="K115" t="n">
+        <v>22000</v>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>-50,000</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>2.04%</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>2.90%</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>+0.86%</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
+        <v>181000</v>
+      </c>
+      <c r="K116" t="n">
+        <v>247000</v>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>66,000</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>8299</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>群聯電子</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>群聯電子</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>0.51%</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>0.22%</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>-0.29%</t>
+        </is>
+      </c>
+      <c r="J117" t="n">
+        <v>24000</v>
+      </c>
+      <c r="K117" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>-14,000</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>2026-09-23_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
           <t>00400A</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>9939</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>宏全</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>0.08%</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="n">
+        <v>180000</v>
+      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>2026-09-23_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2885</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>元大金</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>0.53%</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="n">
+        <v>2241040</v>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>2026-09-23_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>5.41%</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>5.04%</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>-0.37%</t>
+        </is>
+      </c>
+      <c r="J120" t="n">
+        <v>190000</v>
+      </c>
+      <c r="K120" t="n">
+        <v>173000</v>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>-17,000</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>2026-09-23_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
         <is>
           <t>6442</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E121" t="inlineStr">
         <is>
           <t>光 聖</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F121" t="inlineStr">
         <is>
           <t>光 聖</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G121" t="inlineStr">
         <is>
           <t>0.84%</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H121" t="inlineStr">
         <is>
           <t>0.30%</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I121" t="inlineStr">
         <is>
           <t>-0.54%</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="J121" t="n">
         <v>163000</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K121" t="n">
         <v>58000</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L121" t="inlineStr">
         <is>
           <t>-105,000</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M121" t="inlineStr">
         <is>
           <t>2026-09-23_00400A_full_holdings.xlsx</t>
         </is>
